--- a/彩屏Mini-T12【0603封装重置版】（已完结）/bom_彩屏mini-t12【0603封装重置版】带链接 阿南整理和最新bom表一致 (1).xlsx
+++ b/彩屏Mini-T12【0603封装重置版】（已完结）/bom_彩屏mini-t12【0603封装重置版】带链接 阿南整理和最新bom表一致 (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Desktop\复刻计划\烙铁\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Documents\GitHub\open-source-projects\彩屏Mini-T12【0603封装重置版】（已完结）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DAA521-A6A0-4617-9B19-C6A391603C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACAC7DB-CE12-497F-A0AA-7296E92468D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
   <si>
     <t>No</t>
   </si>
@@ -208,6 +208,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>江苏长电</t>
@@ -226,6 +227,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>长晶</t>
@@ -270,6 +272,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>全彩</t>
@@ -288,6 +291,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>带</t>
@@ -306,6 +310,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>正贴</t>
@@ -353,6 +358,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>连接器</t>
@@ -371,6 +377,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>间距翻盖</t>
@@ -433,6 +440,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>弹片</t>
@@ -554,9 +562,6 @@
   </si>
   <si>
     <t>R0603</t>
-  </si>
-  <si>
-    <t>10K</t>
   </si>
   <si>
     <t>KUU</t>
@@ -642,6 +647,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>母座</t>
@@ -660,6 +666,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>板上四脚三次</t>
@@ -830,6 +837,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>,</t>
@@ -1308,6 +1316,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>稳压管</t>
@@ -1343,6 +1352,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>稳压管4.7</t>
@@ -1420,12 +1430,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1439,6 +1451,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1446,6 +1459,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1454,6 +1468,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2497,23 +2512,23 @@
       <c r="E18" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>118</v>
+      <c r="F18" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>115</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="J18" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="J18" s="25" t="s">
+      <c r="K18" s="23" t="s">
         <v>121</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -2524,31 +2539,31 @@
         <v>1</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19" s="12" t="s">
+      <c r="I19" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="J19" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2559,31 +2574,31 @@
         <v>3</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="J20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="K20" s="23" t="s">
         <v>136</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2594,29 +2609,29 @@
         <v>1</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="J21" s="25" t="s">
+      <c r="K21" s="23" t="s">
         <v>144</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2627,25 +2642,25 @@
         <v>1</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>148</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>149</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K22" s="23" t="s">
         <v>150</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2656,29 +2671,29 @@
         <v>1</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>154</v>
-      </c>
       <c r="F23" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J23" s="25" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2689,25 +2704,25 @@
         <v>1</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>159</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>160</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="6"/>
       <c r="J24" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" s="23" t="s">
         <v>161</v>
-      </c>
-      <c r="K24" s="23" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2718,29 +2733,29 @@
         <v>1</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>166</v>
-      </c>
       <c r="G25" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J25" s="27" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -2751,28 +2766,28 @@
         <v>15</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="G26" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H26" s="8" t="s">
+      <c r="I26" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="J26" s="25" t="s">
         <v>174</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2783,31 +2798,31 @@
         <v>1</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E27" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="G27" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J27" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="J27" s="25" t="s">
+      <c r="K27" s="23" t="s">
         <v>180</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2818,31 +2833,31 @@
         <v>2</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="E28" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>184</v>
-      </c>
       <c r="G28" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I28" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J28" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="J28" s="25" t="s">
+      <c r="K28" s="23" t="s">
         <v>186</v>
-      </c>
-      <c r="K28" s="23" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2853,31 +2868,31 @@
         <v>1</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E29" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="G29" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J29" s="29" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2888,31 +2903,31 @@
         <v>2</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="E30" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I30" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J30" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="K30" s="23" t="s">
         <v>198</v>
-      </c>
-      <c r="K30" s="23" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -2923,31 +2938,31 @@
         <v>2</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="G31" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="J31" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="J31" s="27" t="s">
-        <v>204</v>
-      </c>
       <c r="K31" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -2958,28 +2973,28 @@
         <v>4</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>206</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F32" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="H32" s="8" t="s">
+      <c r="I32" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="J32" s="25" t="s">
         <v>209</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -2990,28 +3005,28 @@
         <v>2</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F33" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="I33" s="6" t="s">
+      <c r="J33" s="25" t="s">
         <v>214</v>
-      </c>
-      <c r="J33" s="25" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -3021,19 +3036,19 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>117</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -3043,13 +3058,13 @@
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -3064,28 +3079,28 @@
         <v>1</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F36" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="J36" s="25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -3095,17 +3110,17 @@
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -3116,28 +3131,28 @@
         <v>7</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>226</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>227</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F38" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>229</v>
-      </c>
       <c r="J38" s="25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -3148,26 +3163,26 @@
         <v>1</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3178,31 +3193,31 @@
         <v>2</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F40" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="G40" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I40" s="6" t="s">
+      <c r="J40" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="J40" s="25" t="s">
+      <c r="K40" s="23" t="s">
         <v>236</v>
-      </c>
-      <c r="K40" s="23" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
@@ -3213,26 +3228,26 @@
         <v>1</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -3243,26 +3258,26 @@
         <v>1</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -3273,28 +3288,28 @@
         <v>3</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F43" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="G43" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>244</v>
-      </c>
       <c r="J43" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -3305,31 +3320,31 @@
         <v>15</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H44" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="J44" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="J44" s="25" t="s">
+      <c r="K44" s="24" t="s">
         <v>249</v>
-      </c>
-      <c r="K44" s="24" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -3340,28 +3355,28 @@
         <v>1</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F45" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="G45" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="J45" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
@@ -3372,28 +3387,28 @@
         <v>1</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F46" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>258</v>
-      </c>
       <c r="J46" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
@@ -3404,28 +3419,28 @@
         <v>1</v>
       </c>
       <c r="C47" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F47" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I47" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>262</v>
-      </c>
       <c r="J47" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
@@ -3436,28 +3451,28 @@
         <v>2</v>
       </c>
       <c r="C48" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>263</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>264</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>117</v>
       </c>
       <c r="F48" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I48" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="G48" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>266</v>
-      </c>
       <c r="J48" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3468,13 +3483,13 @@
         <v>1</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>269</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
@@ -3484,13 +3499,13 @@
         <v>55</v>
       </c>
       <c r="I49" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J49" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="J49" s="27" t="s">
+      <c r="K49" s="23" t="s">
         <v>271</v>
-      </c>
-      <c r="K49" s="23" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3501,29 +3516,29 @@
         <v>2</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D50" s="14" t="s">
-        <v>274</v>
-      </c>
       <c r="E50" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I50" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="J50" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="J50" s="27" t="s">
+      <c r="K50" s="23" t="s">
         <v>277</v>
-      </c>
-      <c r="K50" s="23" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3534,27 +3549,27 @@
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="E51" s="8" t="s">
         <v>280</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H51" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="K51" s="23" t="s">
         <v>284</v>
-      </c>
-      <c r="K51" s="23" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
@@ -3565,26 +3580,26 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3595,29 +3610,29 @@
         <v>1</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="F53" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="F53" s="8" t="s">
-        <v>291</v>
-      </c>
       <c r="G53" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="J53" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="J53" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="K53" s="24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3628,29 +3643,29 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D54" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="E54" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>296</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J54" s="25" t="s">
         <v>16</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3661,27 +3676,27 @@
         <v>1</v>
       </c>
       <c r="C55" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D55" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="E55" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>302</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H55" s="6"/>
       <c r="I55" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="J55" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="J55" s="25" t="s">
+      <c r="K55" s="23" t="s">
         <v>304</v>
-      </c>
-      <c r="K55" s="23" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3692,25 +3707,25 @@
         <v>1</v>
       </c>
       <c r="C56" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D56" s="20" t="s">
         <v>300</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>301</v>
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H56" s="6"/>
       <c r="I56" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J56" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K56" s="24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" x14ac:dyDescent="0.3">
@@ -3718,18 +3733,18 @@
         <v>1</v>
       </c>
       <c r="C57" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="J57" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="K57" s="23" t="s">
         <v>308</v>
-      </c>
-      <c r="K57" s="23" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J59" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3789,19 +3804,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" t="s">
         <v>311</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>312</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>313</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>314</v>
-      </c>
-      <c r="E1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4460,7 +4475,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
@@ -4475,7 +4490,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B18" s="1">
         <v>6</v>
@@ -4485,7 +4500,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" s="1">
         <v>20</v>
@@ -4502,7 +4517,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B20" s="3">
         <v>7</v>
@@ -4520,7 +4535,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="3">
         <v>6</v>
@@ -4555,7 +4570,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B23" s="1">
         <v>5</v>
@@ -4591,7 +4606,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="1">
         <v>150</v>
@@ -4601,7 +4616,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B26" s="4">
         <v>50</v>
@@ -4616,7 +4631,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B27" s="4">
         <v>50</v>
@@ -4631,7 +4646,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B28" s="1">
         <v>100</v>
@@ -4646,7 +4661,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B29" s="1">
         <v>100</v>
@@ -4661,7 +4676,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B30" s="1">
         <v>100</v>
@@ -4676,7 +4691,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" s="1">
         <v>18</v>
@@ -4689,7 +4704,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" s="1">
         <v>38</v>
@@ -4699,7 +4714,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -4713,7 +4728,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B35" s="1">
         <v>38</v>
@@ -4723,7 +4738,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -4731,7 +4746,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B37" s="1">
         <v>20</v>
@@ -4743,7 +4758,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B38" s="1">
         <v>20</v>
@@ -4753,7 +4768,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B39" s="1">
         <v>100</v>
@@ -4768,7 +4783,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B40" s="1">
         <v>38</v>
@@ -4779,7 +4794,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B41" s="1">
         <v>38</v>
@@ -4790,7 +4805,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B42" s="1">
         <v>20</v>
@@ -4801,7 +4816,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B43" s="1">
         <v>100</v>
@@ -4816,7 +4831,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B44" s="1">
         <v>20</v>
@@ -4827,7 +4842,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B45" s="1">
         <v>20</v>
@@ -4838,7 +4853,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B46" s="1">
         <v>20</v>
@@ -4849,7 +4864,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B47" s="1">
         <v>20</v>
@@ -4860,7 +4875,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B48" s="1">
         <v>20</v>
@@ -4875,7 +4890,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B49" s="1">
         <v>20</v>
@@ -4890,7 +4905,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B50" s="3">
         <v>8</v>
@@ -4906,7 +4921,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B51" s="1">
         <v>20</v>
@@ -4916,7 +4931,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B52" s="1">
         <v>10</v>
@@ -4940,7 +4955,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B54" s="3">
         <v>6</v>
